--- a/data/data_shichigawahama_w2.xlsx
+++ b/data/data_shichigawahama_w2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AC4E69-02AA-456C-86F3-BA32950EBEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12B0E71-18B9-4ADE-95DE-A4D0B0A9C319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -734,52 +734,16 @@
     <t>相澤憲彦</t>
   </si>
   <si>
-    <t>相澤幸喜</t>
-  </si>
-  <si>
     <t>赤間秋夫</t>
   </si>
   <si>
     <t>赤間陽</t>
   </si>
   <si>
-    <t>赤間胞治</t>
-    <rPh sb="2" eb="3">
-      <t>ホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>赤間英亀</t>
   </si>
   <si>
     <t>赤間三五郎</t>
-  </si>
-  <si>
-    <t>赤間長和</t>
-    <rPh sb="0" eb="2">
-      <t>アカマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>赤間長正</t>
-    <rPh sb="0" eb="2">
-      <t>アカマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ナガ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>マサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>赤間日出男</t>
@@ -807,32 +771,12 @@
     <t>和泉正榮</t>
   </si>
   <si>
-    <t>和泉とも子</t>
-    <rPh sb="4" eb="5">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>伊丹克已</t>
-  </si>
-  <si>
     <t>伊丹勝義</t>
   </si>
   <si>
     <t>伊藤カヅ子</t>
   </si>
   <si>
-    <t>伊藤新一</t>
-    <rPh sb="0" eb="2">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シンイチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>稲妻克夫</t>
   </si>
   <si>
@@ -854,25 +798,9 @@
     <t>遠藤みつ</t>
   </si>
   <si>
-    <t>遠藤やゑ子</t>
-  </si>
-  <si>
-    <t>小野和子</t>
-    <rPh sb="0" eb="2">
-      <t>オノ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カズコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>小野今朝治</t>
   </si>
   <si>
-    <t>小野善右エ門</t>
-  </si>
-  <si>
     <t>加藤勝美</t>
   </si>
   <si>
@@ -882,35 +810,15 @@
     <t>加藤壽治</t>
   </si>
   <si>
-    <t>鎌田多恵子</t>
-    <rPh sb="2" eb="5">
-      <t>タエコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>紀野國正勝</t>
   </si>
   <si>
     <t>小玉智惠</t>
   </si>
   <si>
-    <t>小玉祐樹</t>
-    <rPh sb="2" eb="4">
-      <t>ユウキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>後藤忠男</t>
   </si>
   <si>
-    <t>齋藤勝良</t>
-  </si>
-  <si>
-    <t>齋藤喜良</t>
-  </si>
-  <si>
     <t>齋藤庄英</t>
   </si>
   <si>
@@ -923,26 +831,9 @@
     <t>佐藤勲</t>
   </si>
   <si>
-    <t>佐藤一郎</t>
-    <rPh sb="2" eb="4">
-      <t>イチロウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>佐藤栄二</t>
-  </si>
-  <si>
     <t>佐藤欣一</t>
   </si>
   <si>
-    <t>佐藤幸志</t>
-    <rPh sb="1" eb="2">
-      <t>トウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>佐藤庄司</t>
   </si>
   <si>
@@ -956,13 +847,6 @@
   </si>
   <si>
     <t>佐藤武志</t>
-  </si>
-  <si>
-    <t>佐藤太郎</t>
-    <rPh sb="2" eb="4">
-      <t>タロウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>佐藤照夫</t>
@@ -981,19 +865,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>佐藤兵藏</t>
-  </si>
-  <si>
-    <t>佐藤寛之</t>
-    <rPh sb="3" eb="4">
-      <t>ユキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>佐藤正夫</t>
-  </si>
-  <si>
     <t>佐藤泰夫</t>
   </si>
   <si>
@@ -1032,13 +903,6 @@
   </si>
   <si>
     <t>鈴木清弘</t>
-  </si>
-  <si>
-    <t>鈴木今朝治</t>
-    <rPh sb="2" eb="3">
-      <t>イマ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>鈴木けさよ</t>
@@ -1099,22 +963,12 @@
     <t>鈴木久</t>
   </si>
   <si>
-    <t>鈴木英明</t>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鈴木平捷</t>
   </si>
   <si>
     <t>鈴木ふかよ</t>
   </si>
   <si>
-    <t>鈴木平悦</t>
-  </si>
-  <si>
     <t>鈴木平規</t>
   </si>
   <si>
@@ -1124,13 +978,6 @@
     <t>鈴木益幸</t>
   </si>
   <si>
-    <t>鈴木豊</t>
-    <rPh sb="2" eb="3">
-      <t>ユタカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>鈴木吉秋</t>
   </si>
   <si>
@@ -1143,9 +990,6 @@
     <t>瀬戸秀壽</t>
   </si>
   <si>
-    <t>高橋榮吉</t>
-  </si>
-  <si>
     <t>太宰良子</t>
   </si>
   <si>
@@ -1161,26 +1005,12 @@
     <t>仁田勇</t>
   </si>
   <si>
-    <t>仁田和廣</t>
-    <rPh sb="3" eb="4">
-      <t>ヒロシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>仁田勝昭</t>
   </si>
   <si>
     <t>星新藏</t>
   </si>
   <si>
-    <t>星あい</t>
-    <rPh sb="0" eb="1">
-      <t>ホシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>星榮一</t>
   </si>
   <si>
@@ -1193,36 +1023,15 @@
     <t>星幸吉</t>
   </si>
   <si>
-    <t>星治右衛門</t>
-    <rPh sb="3" eb="4">
-      <t>エイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>星成</t>
   </si>
   <si>
     <t>星正</t>
   </si>
   <si>
-    <t>星辰男</t>
-    <rPh sb="1" eb="3">
-      <t>タツオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>星長一</t>
   </si>
   <si>
-    <t>星博</t>
-    <rPh sb="1" eb="2">
-      <t>ヒロシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>星兵喜</t>
   </si>
   <si>
@@ -1235,58 +1044,21 @@
     <t>星光良</t>
   </si>
   <si>
-    <t>松野明</t>
-    <rPh sb="0" eb="2">
-      <t>マツノ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>アキラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>三浦たつよ</t>
   </si>
   <si>
     <t>三浦門吉</t>
   </si>
   <si>
-    <t>三浦康市</t>
-    <rPh sb="3" eb="4">
-      <t>イチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>三嶋重昭</t>
   </si>
   <si>
-    <t>三島知惠子</t>
-  </si>
-  <si>
     <t>最上明</t>
   </si>
   <si>
     <t>最上實</t>
   </si>
   <si>
-    <t>吉田時男</t>
-    <rPh sb="0" eb="1">
-      <t>ヨシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>米茂夫</t>
-    <rPh sb="1" eb="2">
-      <t>シゲ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>米善藏</t>
-  </si>
-  <si>
     <t>我妻周悦</t>
   </si>
   <si>
@@ -1303,76 +1075,6 @@
   </si>
   <si>
     <t>我妻幸貞</t>
-  </si>
-  <si>
-    <t>渡辺幸一</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウイチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡邊卯之松</t>
-  </si>
-  <si>
-    <t>渡邊栄一</t>
-    <rPh sb="2" eb="4">
-      <t>エイイチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡邊一好</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡邊喜一</t>
-  </si>
-  <si>
-    <t>渡邊繁雄</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡邊庄哉</t>
-  </si>
-  <si>
-    <t>渡邊丹治</t>
-  </si>
-  <si>
-    <t>渡邊留四郎</t>
-  </si>
-  <si>
-    <t>渡邊信雄</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡邉弘</t>
-    <rPh sb="2" eb="3">
-      <t>ヒロシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡邊ふじ江</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>エ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>渡邉勇一郎</t>
@@ -1385,114 +1087,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>渡邊米雄</t>
-    <rPh sb="2" eb="4">
-      <t>ヨネオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>遠藤善兵衛</t>
-    <rPh sb="0" eb="2">
-      <t>エンドウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヘイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>エイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>星章夫</t>
-    <rPh sb="0" eb="1">
-      <t>ホシ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>アキオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鈴木竹浩</t>
-    <rPh sb="0" eb="2">
-      <t>スズキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>タケ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヒロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鈴木長司</t>
-    <rPh sb="0" eb="2">
-      <t>スズキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ツカサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>吉田茂</t>
-    <rPh sb="0" eb="2">
-      <t>ヨシダ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シゲ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>伊藤定栄</t>
-    <rPh sb="0" eb="2">
-      <t>イトウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>サダ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>エイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>赤間善勝</t>
-    <rPh sb="0" eb="2">
-      <t>アカマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ゼン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>カツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡邊傳明</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>デン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>星健二</t>
     <rPh sb="0" eb="1">
       <t>ホシ</t>
@@ -1503,99 +1097,215 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>相沢幸喜</t>
+  </si>
+  <si>
+    <t>赤間胞治</t>
+  </si>
+  <si>
+    <t>赤間長和</t>
+  </si>
+  <si>
+    <t>赤間長正</t>
+  </si>
+  <si>
+    <t>和泉とも子</t>
+  </si>
+  <si>
+    <t>伊丹克己</t>
+  </si>
+  <si>
+    <t>伊藤新一</t>
+  </si>
+  <si>
+    <t>遠藤やえ子</t>
+  </si>
+  <si>
+    <t>小野和子</t>
+  </si>
+  <si>
+    <t>小野善右衞門</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>鎌田多恵子</t>
+  </si>
+  <si>
+    <t>小玉祐樹</t>
+  </si>
+  <si>
+    <t>斉藤勝良</t>
+  </si>
+  <si>
+    <t>齋藤喜良</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>佐藤一郎</t>
+  </si>
+  <si>
+    <t>佐藤榮二</t>
+  </si>
+  <si>
+    <t>佐藤幸志</t>
+  </si>
+  <si>
+    <t>佐藤太郎</t>
+  </si>
+  <si>
+    <t>佐藤兵蔵</t>
+  </si>
+  <si>
+    <t>佐藤寛之</t>
+  </si>
+  <si>
+    <t>佐藤正夫　</t>
+  </si>
+  <si>
+    <t>鈴木今朝治</t>
+  </si>
+  <si>
+    <t>鈴木英明</t>
+  </si>
+  <si>
+    <t>鈴木豊</t>
+  </si>
+  <si>
+    <t>高橋栄吉</t>
+  </si>
+  <si>
+    <t>仁田和廣</t>
+  </si>
+  <si>
+    <t>星あい</t>
+  </si>
+  <si>
+    <t>星治右衛門</t>
+  </si>
+  <si>
+    <t>星辰男</t>
+  </si>
+  <si>
+    <t>星博</t>
+  </si>
+  <si>
+    <t>松野明</t>
+  </si>
+  <si>
+    <t>三浦康市</t>
+  </si>
+  <si>
+    <t>三島知恵子</t>
+  </si>
+  <si>
+    <t>吉田時男</t>
+  </si>
+  <si>
+    <t>米茂夫</t>
+  </si>
+  <si>
+    <t>米善蔵</t>
+  </si>
+  <si>
+    <t>渡辺幸一</t>
+  </si>
+  <si>
+    <t>渡辺卯之松</t>
+  </si>
+  <si>
+    <t>渡辺栄一</t>
+  </si>
+  <si>
+    <t>渡辺一好</t>
+  </si>
+  <si>
+    <t>渡辺喜一</t>
+  </si>
+  <si>
+    <t>渡辺繁雄</t>
+  </si>
+  <si>
+    <t>渡辺庄哉</t>
+  </si>
+  <si>
+    <t>渡辺丹治</t>
+  </si>
+  <si>
+    <t>渡辺留四郎</t>
+  </si>
+  <si>
+    <t>渡辺信雄</t>
+  </si>
+  <si>
+    <t>渡辺弘</t>
+  </si>
+  <si>
+    <t>渡辺ふじ江</t>
+  </si>
+  <si>
+    <t>渡辺米雄</t>
+  </si>
+  <si>
+    <t>遠藤善兵衛</t>
+  </si>
+  <si>
+    <t>星章夫</t>
+  </si>
+  <si>
+    <t>鈴木竹浩</t>
+  </si>
+  <si>
+    <t>鈴木長司</t>
+  </si>
+  <si>
+    <t>吉田茂</t>
+  </si>
+  <si>
+    <t>伊藤定榮</t>
+  </si>
+  <si>
+    <t>赤間善勝</t>
+  </si>
+  <si>
+    <t>渡辺傳明</t>
+  </si>
+  <si>
     <t>赤間竹喜</t>
-    <rPh sb="0" eb="2">
-      <t>アカマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>タケ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>斎藤久</t>
-    <rPh sb="0" eb="2">
-      <t>サイトウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヒサシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>齋藤久</t>
   </si>
   <si>
     <t>松野兵次郎</t>
-    <rPh sb="0" eb="2">
-      <t>マツノ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
+  </si>
+  <si>
+    <t>渡辺俊道</t>
+  </si>
+  <si>
+    <t>佐藤今朝衞</t>
+  </si>
+  <si>
+    <t>三浦和子</t>
+  </si>
+  <si>
+    <t>加藤信勝</t>
+  </si>
+  <si>
+    <t>鈴木実（平悦）</t>
+    <rPh sb="4" eb="5">
       <t>ヘイ</t>
     </rPh>
-    <rPh sb="3" eb="4">
-      <t>ジ</t>
+    <rPh sb="5" eb="6">
+      <t>エツ</t>
     </rPh>
-    <rPh sb="4" eb="5">
-      <t>ロウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>渡辺俊道</t>
-    <rPh sb="0" eb="2">
-      <t>ワタナベ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>シュン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ミチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>佐藤今朝衛</t>
-    <rPh sb="0" eb="2">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ケサ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>エイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>三浦和子</t>
-    <rPh sb="0" eb="2">
-      <t>ミウラ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カズコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>加藤信勝</t>
-    <rPh sb="0" eb="2">
-      <t>カトウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ノブ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>カツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1614,6 +1324,22 @@
       <sz val="6"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1638,13 +1364,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1923,7 +1673,6 @@
   <dimension ref="A1:BE178"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="67.4140625" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="28.5" bestFit="1" customWidth="1"/>
@@ -2155,7 +1904,7 @@
       </c>
     </row>
     <row r="2" spans="1:57">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>209</v>
       </c>
       <c r="B2" t="s">
@@ -2229,7 +1978,7 @@
       </c>
     </row>
     <row r="3" spans="1:57">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>210</v>
       </c>
       <c r="B3" t="s">
@@ -2267,7 +2016,7 @@
       </c>
     </row>
     <row r="4" spans="1:57">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>211</v>
       </c>
       <c r="B4" t="s">
@@ -2311,7 +2060,7 @@
       </c>
     </row>
     <row r="5" spans="1:57">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B5" t="s">
@@ -2346,8 +2095,8 @@
       </c>
     </row>
     <row r="6" spans="1:57">
-      <c r="A6" t="s">
-        <v>213</v>
+      <c r="A6" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -2396,8 +2145,8 @@
       </c>
     </row>
     <row r="7" spans="1:57">
-      <c r="A7" t="s">
-        <v>214</v>
+      <c r="A7" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="B7" t="s">
         <v>197</v>
@@ -2443,8 +2192,8 @@
       </c>
     </row>
     <row r="8" spans="1:57">
-      <c r="A8" t="s">
-        <v>215</v>
+      <c r="A8" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="B8" t="s">
         <v>199</v>
@@ -2493,8 +2242,8 @@
       </c>
     </row>
     <row r="9" spans="1:57">
-      <c r="A9" t="s">
-        <v>216</v>
+      <c r="A9" s="1" t="s">
+        <v>321</v>
       </c>
       <c r="B9" t="s">
         <v>182</v>
@@ -2552,8 +2301,8 @@
       </c>
     </row>
     <row r="10" spans="1:57">
-      <c r="A10" t="s">
-        <v>217</v>
+      <c r="A10" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -2587,8 +2336,8 @@
       </c>
     </row>
     <row r="11" spans="1:57">
-      <c r="A11" t="s">
-        <v>218</v>
+      <c r="A11" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="B11" t="s">
         <v>60</v>
@@ -2637,8 +2386,8 @@
       </c>
     </row>
     <row r="12" spans="1:57">
-      <c r="A12" t="s">
-        <v>219</v>
+      <c r="A12" s="1" t="s">
+        <v>322</v>
       </c>
       <c r="B12" t="s">
         <v>183</v>
@@ -2675,8 +2424,8 @@
       </c>
     </row>
     <row r="13" spans="1:57">
-      <c r="A13" t="s">
-        <v>220</v>
+      <c r="A13" s="1" t="s">
+        <v>323</v>
       </c>
       <c r="B13" t="s">
         <v>61</v>
@@ -2728,8 +2477,8 @@
       </c>
     </row>
     <row r="14" spans="1:57">
-      <c r="A14" t="s">
-        <v>221</v>
+      <c r="A14" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="B14" t="s">
         <v>200</v>
@@ -2772,8 +2521,8 @@
       </c>
     </row>
     <row r="15" spans="1:57">
-      <c r="A15" t="s">
-        <v>222</v>
+      <c r="A15" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="B15" t="s">
         <v>62</v>
@@ -2813,8 +2562,8 @@
       </c>
     </row>
     <row r="16" spans="1:57">
-      <c r="A16" t="s">
-        <v>223</v>
+      <c r="A16" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="B16" t="s">
         <v>63</v>
@@ -2842,8 +2591,8 @@
       </c>
     </row>
     <row r="17" spans="1:57">
-      <c r="A17" t="s">
-        <v>224</v>
+      <c r="A17" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="B17" t="s">
         <v>197</v>
@@ -2871,8 +2620,8 @@
       </c>
     </row>
     <row r="18" spans="1:57">
-      <c r="A18" t="s">
-        <v>225</v>
+      <c r="A18" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="B18" t="s">
         <v>64</v>
@@ -2909,8 +2658,8 @@
       </c>
     </row>
     <row r="19" spans="1:57">
-      <c r="A19" t="s">
-        <v>226</v>
+      <c r="A19" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B19" t="s">
         <v>201</v>
@@ -2983,8 +2732,8 @@
       </c>
     </row>
     <row r="20" spans="1:57">
-      <c r="A20" t="s">
-        <v>227</v>
+      <c r="A20" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="B20" t="s">
         <v>65</v>
@@ -3018,8 +2767,8 @@
       </c>
     </row>
     <row r="21" spans="1:57">
-      <c r="A21" t="s">
-        <v>228</v>
+      <c r="A21" s="1" t="s">
+        <v>325</v>
       </c>
       <c r="B21" t="s">
         <v>184</v>
@@ -3056,8 +2805,8 @@
       </c>
     </row>
     <row r="22" spans="1:57">
-      <c r="A22" t="s">
-        <v>229</v>
+      <c r="A22" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="B22" t="s">
         <v>66</v>
@@ -3085,8 +2834,8 @@
       </c>
     </row>
     <row r="23" spans="1:57">
-      <c r="A23" t="s">
-        <v>230</v>
+      <c r="A23" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="B23" t="s">
         <v>67</v>
@@ -3123,8 +2872,8 @@
       </c>
     </row>
     <row r="24" spans="1:57">
-      <c r="A24" t="s">
-        <v>231</v>
+      <c r="A24" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="B24" t="s">
         <v>185</v>
@@ -3161,8 +2910,8 @@
       </c>
     </row>
     <row r="25" spans="1:57">
-      <c r="A25" t="s">
-        <v>232</v>
+      <c r="A25" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="B25" t="s">
         <v>197</v>
@@ -3202,8 +2951,8 @@
       </c>
     </row>
     <row r="26" spans="1:57">
-      <c r="A26" t="s">
-        <v>233</v>
+      <c r="A26" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="B26" t="s">
         <v>68</v>
@@ -3243,8 +2992,8 @@
       </c>
     </row>
     <row r="27" spans="1:57">
-      <c r="A27" t="s">
-        <v>234</v>
+      <c r="A27" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="B27" t="s">
         <v>69</v>
@@ -3284,8 +3033,8 @@
       </c>
     </row>
     <row r="28" spans="1:57">
-      <c r="A28" t="s">
-        <v>235</v>
+      <c r="A28" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="B28" t="s">
         <v>70</v>
@@ -3322,8 +3071,8 @@
       </c>
     </row>
     <row r="29" spans="1:57">
-      <c r="A29" t="s">
-        <v>236</v>
+      <c r="A29" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="B29" t="s">
         <v>71</v>
@@ -3366,8 +3115,8 @@
       </c>
     </row>
     <row r="30" spans="1:57">
-      <c r="A30" t="s">
-        <v>237</v>
+      <c r="A30" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="B30" t="s">
         <v>72</v>
@@ -3395,8 +3144,8 @@
       </c>
     </row>
     <row r="31" spans="1:57">
-      <c r="A31" t="s">
-        <v>238</v>
+      <c r="A31" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="B31" t="s">
         <v>198</v>
@@ -3427,8 +3176,8 @@
       </c>
     </row>
     <row r="32" spans="1:57">
-      <c r="A32" t="s">
-        <v>239</v>
+      <c r="A32" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="B32" t="s">
         <v>198</v>
@@ -3474,8 +3223,8 @@
       </c>
     </row>
     <row r="33" spans="1:57">
-      <c r="A33" t="s">
-        <v>240</v>
+      <c r="A33" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="B33" t="s">
         <v>73</v>
@@ -3515,8 +3264,8 @@
       </c>
     </row>
     <row r="34" spans="1:57">
-      <c r="A34" t="s">
-        <v>241</v>
+      <c r="A34" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="B34" t="s">
         <v>74</v>
@@ -3544,8 +3293,8 @@
       </c>
     </row>
     <row r="35" spans="1:57">
-      <c r="A35" t="s">
-        <v>242</v>
+      <c r="A35" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="B35" t="s">
         <v>202</v>
@@ -3618,8 +3367,8 @@
       </c>
     </row>
     <row r="36" spans="1:57">
-      <c r="A36" t="s">
-        <v>243</v>
+      <c r="A36" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="B36" t="s">
         <v>75</v>
@@ -3656,8 +3405,8 @@
       </c>
     </row>
     <row r="37" spans="1:57">
-      <c r="A37" t="s">
-        <v>244</v>
+      <c r="A37" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="B37" t="s">
         <v>197</v>
@@ -3727,8 +3476,8 @@
       </c>
     </row>
     <row r="38" spans="1:57">
-      <c r="A38" t="s">
-        <v>245</v>
+      <c r="A38" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="B38" t="s">
         <v>76</v>
@@ -3762,8 +3511,8 @@
       </c>
     </row>
     <row r="39" spans="1:57">
-      <c r="A39" t="s">
-        <v>246</v>
+      <c r="A39" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="B39" t="s">
         <v>198</v>
@@ -3803,8 +3552,8 @@
       </c>
     </row>
     <row r="40" spans="1:57">
-      <c r="A40" t="s">
-        <v>247</v>
+      <c r="A40" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="B40" t="s">
         <v>77</v>
@@ -3847,8 +3596,8 @@
       </c>
     </row>
     <row r="41" spans="1:57">
-      <c r="A41" t="s">
-        <v>248</v>
+      <c r="A41" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="B41" t="s">
         <v>78</v>
@@ -3888,8 +3637,8 @@
       </c>
     </row>
     <row r="42" spans="1:57">
-      <c r="A42" t="s">
-        <v>249</v>
+      <c r="A42" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="B42" t="s">
         <v>186</v>
@@ -3935,8 +3684,8 @@
       </c>
     </row>
     <row r="43" spans="1:57">
-      <c r="A43" t="s">
-        <v>250</v>
+      <c r="A43" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="B43" t="s">
         <v>79</v>
@@ -3967,8 +3716,8 @@
       </c>
     </row>
     <row r="44" spans="1:57">
-      <c r="A44" t="s">
-        <v>251</v>
+      <c r="A44" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="B44" t="s">
         <v>203</v>
@@ -4018,7 +3767,7 @@
     </row>
     <row r="45" spans="1:57">
       <c r="A45" t="s">
-        <v>252</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s">
         <v>80</v>
@@ -4076,8 +3825,8 @@
       </c>
     </row>
     <row r="46" spans="1:57">
-      <c r="A46" t="s">
-        <v>253</v>
+      <c r="A46" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="B46" t="s">
         <v>81</v>
@@ -4150,8 +3899,8 @@
       </c>
     </row>
     <row r="47" spans="1:57">
-      <c r="A47" t="s">
-        <v>254</v>
+      <c r="A47" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="B47" t="s">
         <v>204</v>
@@ -4209,8 +3958,8 @@
       </c>
     </row>
     <row r="48" spans="1:57">
-      <c r="A48" t="s">
-        <v>255</v>
+      <c r="A48" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="B48" t="s">
         <v>82</v>
@@ -4244,8 +3993,8 @@
       </c>
     </row>
     <row r="49" spans="1:57">
-      <c r="A49" t="s">
-        <v>256</v>
+      <c r="A49" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="B49" t="s">
         <v>197</v>
@@ -4303,8 +4052,8 @@
       </c>
     </row>
     <row r="50" spans="1:57">
-      <c r="A50" t="s">
-        <v>257</v>
+      <c r="A50" s="1" t="s">
+        <v>334</v>
       </c>
       <c r="B50" t="s">
         <v>197</v>
@@ -4374,8 +4123,8 @@
       </c>
     </row>
     <row r="51" spans="1:57">
-      <c r="A51" t="s">
-        <v>258</v>
+      <c r="A51" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="B51" t="s">
         <v>83</v>
@@ -4403,8 +4152,8 @@
       </c>
     </row>
     <row r="52" spans="1:57">
-      <c r="A52" t="s">
-        <v>259</v>
+      <c r="A52" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="B52" t="s">
         <v>197</v>
@@ -4465,8 +4214,8 @@
       </c>
     </row>
     <row r="53" spans="1:57">
-      <c r="A53" t="s">
-        <v>260</v>
+      <c r="A53" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="B53" t="s">
         <v>187</v>
@@ -4503,8 +4252,8 @@
       </c>
     </row>
     <row r="54" spans="1:57">
-      <c r="A54" t="s">
-        <v>261</v>
+      <c r="A54" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="B54" t="s">
         <v>84</v>
@@ -4532,8 +4281,8 @@
       </c>
     </row>
     <row r="55" spans="1:57">
-      <c r="A55" t="s">
-        <v>262</v>
+      <c r="A55" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="B55" t="s">
         <v>85</v>
@@ -4570,8 +4319,8 @@
       </c>
     </row>
     <row r="56" spans="1:57">
-      <c r="A56" t="s">
-        <v>263</v>
+      <c r="A56" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="B56" t="s">
         <v>86</v>
@@ -4615,7 +4364,7 @@
     </row>
     <row r="57" spans="1:57">
       <c r="A57" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="B57" t="s">
         <v>87</v>
@@ -4646,8 +4395,8 @@
       </c>
     </row>
     <row r="58" spans="1:57">
-      <c r="A58" t="s">
-        <v>265</v>
+      <c r="A58" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="B58" t="s">
         <v>88</v>
@@ -4681,8 +4430,8 @@
       </c>
     </row>
     <row r="59" spans="1:57">
-      <c r="A59" t="s">
-        <v>266</v>
+      <c r="A59" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="B59" t="s">
         <v>89</v>
@@ -4752,8 +4501,8 @@
       </c>
     </row>
     <row r="60" spans="1:57">
-      <c r="A60" t="s">
-        <v>267</v>
+      <c r="A60" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="B60" t="s">
         <v>90</v>
@@ -4791,7 +4540,7 @@
     </row>
     <row r="61" spans="1:57">
       <c r="A61" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="B61" t="s">
         <v>91</v>
@@ -4822,8 +4571,8 @@
       </c>
     </row>
     <row r="62" spans="1:57">
-      <c r="A62" t="s">
-        <v>269</v>
+      <c r="A62" s="1" t="s">
+        <v>338</v>
       </c>
       <c r="B62" t="s">
         <v>92</v>
@@ -4857,8 +4606,8 @@
       </c>
     </row>
     <row r="63" spans="1:57">
-      <c r="A63" t="s">
-        <v>270</v>
+      <c r="A63" s="1" t="s">
+        <v>339</v>
       </c>
       <c r="B63" t="s">
         <v>93</v>
@@ -4892,8 +4641,8 @@
       </c>
     </row>
     <row r="64" spans="1:57">
-      <c r="A64" t="s">
-        <v>271</v>
+      <c r="A64" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="B64" t="s">
         <v>94</v>
@@ -4924,8 +4673,8 @@
       </c>
     </row>
     <row r="65" spans="1:57">
-      <c r="A65" t="s">
-        <v>272</v>
+      <c r="A65" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="B65" t="s">
         <v>95</v>
@@ -4995,8 +4744,8 @@
       </c>
     </row>
     <row r="66" spans="1:57">
-      <c r="A66" t="s">
-        <v>273</v>
+      <c r="A66" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="B66" t="s">
         <v>197</v>
@@ -5057,8 +4806,8 @@
       </c>
     </row>
     <row r="67" spans="1:57">
-      <c r="A67" t="s">
-        <v>274</v>
+      <c r="A67" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="B67" t="s">
         <v>96</v>
@@ -5090,7 +4839,7 @@
     </row>
     <row r="68" spans="1:57">
       <c r="A68" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="B68" t="s">
         <v>188</v>
@@ -5121,8 +4870,8 @@
       </c>
     </row>
     <row r="69" spans="1:57">
-      <c r="A69" t="s">
-        <v>276</v>
+      <c r="A69" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="B69" t="s">
         <v>97</v>
@@ -5156,8 +4905,8 @@
       </c>
     </row>
     <row r="70" spans="1:57">
-      <c r="A70" t="s">
-        <v>277</v>
+      <c r="A70" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="B70" t="s">
         <v>98</v>
@@ -5197,8 +4946,8 @@
       </c>
     </row>
     <row r="71" spans="1:57">
-      <c r="A71" t="s">
-        <v>278</v>
+      <c r="A71" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="B71" t="s">
         <v>189</v>
@@ -5265,8 +5014,8 @@
       </c>
     </row>
     <row r="72" spans="1:57">
-      <c r="A72" t="s">
-        <v>279</v>
+      <c r="A72" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="B72" t="s">
         <v>99</v>
@@ -5327,8 +5076,8 @@
       </c>
     </row>
     <row r="73" spans="1:57">
-      <c r="A73" t="s">
-        <v>280</v>
+      <c r="A73" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="B73" t="s">
         <v>205</v>
@@ -5381,7 +5130,7 @@
     </row>
     <row r="74" spans="1:57">
       <c r="A74" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="B74" t="s">
         <v>100</v>
@@ -5412,8 +5161,8 @@
       </c>
     </row>
     <row r="75" spans="1:57">
-      <c r="A75" t="s">
-        <v>282</v>
+      <c r="A75" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="B75" t="s">
         <v>101</v>
@@ -5447,8 +5196,8 @@
       </c>
     </row>
     <row r="76" spans="1:57">
-      <c r="A76" t="s">
-        <v>283</v>
+      <c r="A76" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="B76" t="s">
         <v>102</v>
@@ -5482,8 +5231,8 @@
       </c>
     </row>
     <row r="77" spans="1:57">
-      <c r="A77" t="s">
-        <v>284</v>
+      <c r="A77" s="1" t="s">
+        <v>341</v>
       </c>
       <c r="B77" t="s">
         <v>103</v>
@@ -5517,8 +5266,8 @@
       </c>
     </row>
     <row r="78" spans="1:57">
-      <c r="A78" t="s">
-        <v>285</v>
+      <c r="A78" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="B78" t="s">
         <v>197</v>
@@ -5556,7 +5305,7 @@
     </row>
     <row r="79" spans="1:57">
       <c r="A79" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="B79" t="s">
         <v>104</v>
@@ -5593,8 +5342,8 @@
       </c>
     </row>
     <row r="80" spans="1:57">
-      <c r="A80" t="s">
-        <v>287</v>
+      <c r="A80" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="B80" t="s">
         <v>105</v>
@@ -5625,8 +5374,8 @@
       </c>
     </row>
     <row r="81" spans="1:57">
-      <c r="A81" t="s">
-        <v>288</v>
+      <c r="A81" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="B81" t="s">
         <v>190</v>
@@ -5666,8 +5415,8 @@
       </c>
     </row>
     <row r="82" spans="1:57">
-      <c r="A82" t="s">
-        <v>289</v>
+      <c r="A82" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="B82" t="s">
         <v>202</v>
@@ -5698,8 +5447,8 @@
       </c>
     </row>
     <row r="83" spans="1:57">
-      <c r="A83" t="s">
-        <v>290</v>
+      <c r="A83" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B83" t="s">
         <v>106</v>
@@ -5736,8 +5485,8 @@
       </c>
     </row>
     <row r="84" spans="1:57">
-      <c r="A84" t="s">
-        <v>291</v>
+      <c r="A84" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="B84" t="s">
         <v>107</v>
@@ -5771,8 +5520,8 @@
       </c>
     </row>
     <row r="85" spans="1:57">
-      <c r="A85" t="s">
-        <v>292</v>
+      <c r="A85" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="B85" t="s">
         <v>197</v>
@@ -5809,8 +5558,8 @@
       </c>
     </row>
     <row r="86" spans="1:57">
-      <c r="A86" t="s">
-        <v>293</v>
+      <c r="A86" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="B86" t="s">
         <v>108</v>
@@ -5838,8 +5587,8 @@
       </c>
     </row>
     <row r="87" spans="1:57">
-      <c r="A87" t="s">
-        <v>294</v>
+      <c r="A87" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="B87" t="s">
         <v>109</v>
@@ -5888,8 +5637,8 @@
       </c>
     </row>
     <row r="88" spans="1:57">
-      <c r="A88" t="s">
-        <v>295</v>
+      <c r="A88" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="B88" t="s">
         <v>110</v>
@@ -5923,8 +5672,8 @@
       </c>
     </row>
     <row r="89" spans="1:57">
-      <c r="A89" t="s">
-        <v>296</v>
+      <c r="A89" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="B89" t="s">
         <v>111</v>
@@ -5958,8 +5707,8 @@
       </c>
     </row>
     <row r="90" spans="1:57">
-      <c r="A90" t="s">
-        <v>297</v>
+      <c r="A90" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="B90" t="s">
         <v>112</v>
@@ -5993,8 +5742,8 @@
       </c>
     </row>
     <row r="91" spans="1:57">
-      <c r="A91" t="s">
-        <v>298</v>
+      <c r="A91" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="B91" t="s">
         <v>113</v>
@@ -6034,8 +5783,8 @@
       </c>
     </row>
     <row r="92" spans="1:57">
-      <c r="A92" t="s">
-        <v>299</v>
+      <c r="A92" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="B92" t="s">
         <v>114</v>
@@ -6102,8 +5851,8 @@
       </c>
     </row>
     <row r="93" spans="1:57">
-      <c r="A93" t="s">
-        <v>300</v>
+      <c r="A93" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="B93" t="s">
         <v>197</v>
@@ -6173,8 +5922,8 @@
       </c>
     </row>
     <row r="94" spans="1:57">
-      <c r="A94" t="s">
-        <v>301</v>
+      <c r="A94" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="B94" t="s">
         <v>115</v>
@@ -6211,8 +5960,8 @@
       </c>
     </row>
     <row r="95" spans="1:57">
-      <c r="A95" t="s">
-        <v>302</v>
+      <c r="A95" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="B95" t="s">
         <v>116</v>
@@ -6252,8 +6001,8 @@
       </c>
     </row>
     <row r="96" spans="1:57">
-      <c r="A96" t="s">
-        <v>303</v>
+      <c r="A96" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="B96" t="s">
         <v>117</v>
@@ -6293,8 +6042,8 @@
       </c>
     </row>
     <row r="97" spans="1:57">
-      <c r="A97" t="s">
-        <v>304</v>
+      <c r="A97" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="B97" t="s">
         <v>118</v>
@@ -6334,8 +6083,8 @@
       </c>
     </row>
     <row r="98" spans="1:57">
-      <c r="A98" t="s">
-        <v>305</v>
+      <c r="A98" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="B98" t="s">
         <v>202</v>
@@ -6378,8 +6127,8 @@
       </c>
     </row>
     <row r="99" spans="1:57">
-      <c r="A99" t="s">
-        <v>306</v>
+      <c r="A99" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="B99" t="s">
         <v>191</v>
@@ -6452,8 +6201,8 @@
       </c>
     </row>
     <row r="100" spans="1:57">
-      <c r="A100" t="s">
-        <v>307</v>
+      <c r="A100" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="B100" t="s">
         <v>119</v>
@@ -6487,8 +6236,8 @@
       </c>
     </row>
     <row r="101" spans="1:57">
-      <c r="A101" t="s">
-        <v>308</v>
+      <c r="A101" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="B101" t="s">
         <v>120</v>
@@ -6522,8 +6271,8 @@
       </c>
     </row>
     <row r="102" spans="1:57">
-      <c r="A102" t="s">
-        <v>309</v>
+      <c r="A102" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="B102" t="s">
         <v>121</v>
@@ -6554,8 +6303,8 @@
       </c>
     </row>
     <row r="103" spans="1:57">
-      <c r="A103" t="s">
-        <v>310</v>
+      <c r="A103" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="B103" t="s">
         <v>198</v>
@@ -6622,8 +6371,8 @@
       </c>
     </row>
     <row r="104" spans="1:57">
-      <c r="A104" t="s">
-        <v>311</v>
+      <c r="A104" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="B104" t="s">
         <v>122</v>
@@ -6657,8 +6406,8 @@
       </c>
     </row>
     <row r="105" spans="1:57">
-      <c r="A105" t="s">
-        <v>312</v>
+      <c r="A105" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="B105" t="s">
         <v>123</v>
@@ -6692,8 +6441,8 @@
       </c>
     </row>
     <row r="106" spans="1:57">
-      <c r="A106" t="s">
-        <v>313</v>
+      <c r="A106" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="B106" t="s">
         <v>124</v>
@@ -6727,8 +6476,8 @@
       </c>
     </row>
     <row r="107" spans="1:57">
-      <c r="A107" t="s">
-        <v>314</v>
+      <c r="A107" s="1" t="s">
+        <v>344</v>
       </c>
       <c r="B107" t="s">
         <v>125</v>
@@ -6762,8 +6511,8 @@
       </c>
     </row>
     <row r="108" spans="1:57">
-      <c r="A108" t="s">
-        <v>315</v>
+      <c r="A108" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="B108" t="s">
         <v>126</v>
@@ -6809,8 +6558,8 @@
       </c>
     </row>
     <row r="109" spans="1:57">
-      <c r="A109" t="s">
-        <v>316</v>
+      <c r="A109" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="B109" t="s">
         <v>206</v>
@@ -6850,8 +6599,8 @@
       </c>
     </row>
     <row r="110" spans="1:57">
-      <c r="A110" t="s">
-        <v>317</v>
+      <c r="A110" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="B110" t="s">
         <v>127</v>
@@ -6897,8 +6646,8 @@
       </c>
     </row>
     <row r="111" spans="1:57">
-      <c r="A111" t="s">
-        <v>318</v>
+      <c r="A111" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="B111" t="s">
         <v>197</v>
@@ -6950,8 +6699,8 @@
       </c>
     </row>
     <row r="112" spans="1:57">
-      <c r="A112" t="s">
-        <v>319</v>
+      <c r="A112" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="B112" t="s">
         <v>128</v>
@@ -6991,8 +6740,8 @@
       </c>
     </row>
     <row r="113" spans="1:57">
-      <c r="A113" t="s">
-        <v>320</v>
+      <c r="A113" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="B113" t="s">
         <v>129</v>
@@ -7023,8 +6772,8 @@
       </c>
     </row>
     <row r="114" spans="1:57">
-      <c r="A114" t="s">
-        <v>321</v>
+      <c r="A114" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="B114" t="s">
         <v>130</v>
@@ -7079,8 +6828,8 @@
       </c>
     </row>
     <row r="115" spans="1:57">
-      <c r="A115" t="s">
-        <v>322</v>
+      <c r="A115" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="B115" t="s">
         <v>131</v>
@@ -7114,8 +6863,8 @@
       </c>
     </row>
     <row r="116" spans="1:57">
-      <c r="A116" t="s">
-        <v>323</v>
+      <c r="A116" s="1" t="s">
+        <v>346</v>
       </c>
       <c r="B116" t="s">
         <v>192</v>
@@ -7167,8 +6916,8 @@
       </c>
     </row>
     <row r="117" spans="1:57">
-      <c r="A117" t="s">
-        <v>324</v>
+      <c r="A117" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="B117" t="s">
         <v>132</v>
@@ -7196,8 +6945,8 @@
       </c>
     </row>
     <row r="118" spans="1:57">
-      <c r="A118" t="s">
-        <v>325</v>
+      <c r="A118" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="B118" t="s">
         <v>193</v>
@@ -7234,8 +6983,8 @@
       </c>
     </row>
     <row r="119" spans="1:57">
-      <c r="A119" t="s">
-        <v>326</v>
+      <c r="A119" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="B119" t="s">
         <v>133</v>
@@ -7269,8 +7018,8 @@
       </c>
     </row>
     <row r="120" spans="1:57">
-      <c r="A120" t="s">
-        <v>327</v>
+      <c r="A120" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="B120" t="s">
         <v>134</v>
@@ -7331,8 +7080,8 @@
       </c>
     </row>
     <row r="121" spans="1:57">
-      <c r="A121" t="s">
-        <v>328</v>
+      <c r="A121" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="B121" t="s">
         <v>135</v>
@@ -7366,8 +7115,8 @@
       </c>
     </row>
     <row r="122" spans="1:57">
-      <c r="A122" t="s">
-        <v>329</v>
+      <c r="A122" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="B122" t="s">
         <v>136</v>
@@ -7453,7 +7202,7 @@
     </row>
     <row r="123" spans="1:57">
       <c r="A123" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="B123" t="s">
         <v>204</v>
@@ -7490,8 +7239,8 @@
       </c>
     </row>
     <row r="124" spans="1:57">
-      <c r="A124" t="s">
-        <v>331</v>
+      <c r="A124" s="1" t="s">
+        <v>348</v>
       </c>
       <c r="B124" t="s">
         <v>137</v>
@@ -7528,8 +7277,8 @@
       </c>
     </row>
     <row r="125" spans="1:57">
-      <c r="A125" t="s">
-        <v>332</v>
+      <c r="A125" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="B125" t="s">
         <v>138</v>
@@ -7569,8 +7318,8 @@
       </c>
     </row>
     <row r="126" spans="1:57">
-      <c r="A126" t="s">
-        <v>333</v>
+      <c r="A126" s="1" t="s">
+        <v>349</v>
       </c>
       <c r="B126" t="s">
         <v>139</v>
@@ -7610,8 +7359,8 @@
       </c>
     </row>
     <row r="127" spans="1:57">
-      <c r="A127" t="s">
-        <v>334</v>
+      <c r="A127" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="B127" t="s">
         <v>140</v>
@@ -7642,8 +7391,8 @@
       </c>
     </row>
     <row r="128" spans="1:57">
-      <c r="A128" t="s">
-        <v>335</v>
+      <c r="A128" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="B128" t="s">
         <v>141</v>
@@ -7677,8 +7426,8 @@
       </c>
     </row>
     <row r="129" spans="1:57">
-      <c r="A129" t="s">
-        <v>336</v>
+      <c r="A129" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="B129" t="s">
         <v>142</v>
@@ -7709,8 +7458,8 @@
       </c>
     </row>
     <row r="130" spans="1:57">
-      <c r="A130" t="s">
-        <v>337</v>
+      <c r="A130" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="B130" t="s">
         <v>143</v>
@@ -7744,8 +7493,8 @@
       </c>
     </row>
     <row r="131" spans="1:57">
-      <c r="A131" t="s">
-        <v>338</v>
+      <c r="A131" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="B131" t="s">
         <v>207</v>
@@ -7794,8 +7543,8 @@
       </c>
     </row>
     <row r="132" spans="1:57">
-      <c r="A132" t="s">
-        <v>339</v>
+      <c r="A132" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="B132" t="s">
         <v>208</v>
@@ -7835,8 +7584,8 @@
       </c>
     </row>
     <row r="133" spans="1:57">
-      <c r="A133" t="s">
-        <v>340</v>
+      <c r="A133" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="B133" t="s">
         <v>144</v>
@@ -7888,8 +7637,8 @@
       </c>
     </row>
     <row r="134" spans="1:57">
-      <c r="A134" t="s">
-        <v>341</v>
+      <c r="A134" s="1" t="s">
+        <v>351</v>
       </c>
       <c r="B134" t="s">
         <v>145</v>
@@ -7932,8 +7681,8 @@
       </c>
     </row>
     <row r="135" spans="1:57">
-      <c r="A135" t="s">
-        <v>342</v>
+      <c r="A135" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="B135" t="s">
         <v>146</v>
@@ -8009,8 +7758,8 @@
       </c>
     </row>
     <row r="136" spans="1:57">
-      <c r="A136" t="s">
-        <v>343</v>
+      <c r="A136" s="1" t="s">
+        <v>352</v>
       </c>
       <c r="B136" t="s">
         <v>197</v>
@@ -8056,8 +7805,8 @@
       </c>
     </row>
     <row r="137" spans="1:57">
-      <c r="A137" t="s">
-        <v>344</v>
+      <c r="A137" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="B137" t="s">
         <v>204</v>
@@ -8109,8 +7858,8 @@
       </c>
     </row>
     <row r="138" spans="1:57">
-      <c r="A138" t="s">
-        <v>345</v>
+      <c r="A138" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="B138" t="s">
         <v>147</v>
@@ -8144,8 +7893,8 @@
       </c>
     </row>
     <row r="139" spans="1:57">
-      <c r="A139" t="s">
-        <v>346</v>
+      <c r="A139" s="1" t="s">
+        <v>353</v>
       </c>
       <c r="B139" t="s">
         <v>148</v>
@@ -8182,8 +7931,8 @@
       </c>
     </row>
     <row r="140" spans="1:57">
-      <c r="A140" t="s">
-        <v>347</v>
+      <c r="A140" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="B140" t="s">
         <v>149</v>
@@ -8214,8 +7963,8 @@
       </c>
     </row>
     <row r="141" spans="1:57">
-      <c r="A141" t="s">
-        <v>348</v>
+      <c r="A141" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="B141" t="s">
         <v>197</v>
@@ -8294,8 +8043,8 @@
       </c>
     </row>
     <row r="142" spans="1:57">
-      <c r="A142" t="s">
-        <v>349</v>
+      <c r="A142" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="B142" t="s">
         <v>150</v>
@@ -8335,8 +8084,8 @@
       </c>
     </row>
     <row r="143" spans="1:57">
-      <c r="A143" t="s">
-        <v>350</v>
+      <c r="A143" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="B143" t="s">
         <v>151</v>
@@ -8370,8 +8119,8 @@
       </c>
     </row>
     <row r="144" spans="1:57">
-      <c r="A144" t="s">
-        <v>351</v>
+      <c r="A144" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="B144" t="s">
         <v>152</v>
@@ -8405,8 +8154,8 @@
       </c>
     </row>
     <row r="145" spans="1:57">
-      <c r="A145" t="s">
-        <v>352</v>
+      <c r="A145" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="B145" t="s">
         <v>153</v>
@@ -8449,8 +8198,8 @@
       </c>
     </row>
     <row r="146" spans="1:57">
-      <c r="A146" t="s">
-        <v>353</v>
+      <c r="A146" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="B146" t="s">
         <v>154</v>
@@ -8484,8 +8233,8 @@
       </c>
     </row>
     <row r="147" spans="1:57">
-      <c r="A147" t="s">
-        <v>354</v>
+      <c r="A147" s="1" t="s">
+        <v>317</v>
       </c>
       <c r="B147" t="s">
         <v>155</v>
@@ -8522,8 +8271,8 @@
       </c>
     </row>
     <row r="148" spans="1:57">
-      <c r="A148" t="s">
-        <v>355</v>
+      <c r="A148" s="1" t="s">
+        <v>356</v>
       </c>
       <c r="B148" t="s">
         <v>156</v>
@@ -8560,8 +8309,8 @@
       </c>
     </row>
     <row r="149" spans="1:57">
-      <c r="A149" t="s">
-        <v>356</v>
+      <c r="A149" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="B149" t="s">
         <v>157</v>
@@ -8622,8 +8371,8 @@
       </c>
     </row>
     <row r="150" spans="1:57">
-      <c r="A150" t="s">
-        <v>357</v>
+      <c r="A150" s="1" t="s">
+        <v>358</v>
       </c>
       <c r="B150" t="s">
         <v>158</v>
@@ -8675,8 +8424,8 @@
       </c>
     </row>
     <row r="151" spans="1:57">
-      <c r="A151" t="s">
-        <v>358</v>
+      <c r="A151" s="1" t="s">
+        <v>359</v>
       </c>
       <c r="B151" t="s">
         <v>159</v>
@@ -8707,8 +8456,8 @@
       </c>
     </row>
     <row r="152" spans="1:57">
-      <c r="A152" t="s">
-        <v>359</v>
+      <c r="A152" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="B152" t="s">
         <v>160</v>
@@ -8736,8 +8485,8 @@
       </c>
     </row>
     <row r="153" spans="1:57">
-      <c r="A153" t="s">
-        <v>360</v>
+      <c r="A153" s="1" t="s">
+        <v>361</v>
       </c>
       <c r="B153" t="s">
         <v>194</v>
@@ -8810,8 +8559,8 @@
       </c>
     </row>
     <row r="154" spans="1:57">
-      <c r="A154" t="s">
-        <v>361</v>
+      <c r="A154" s="1" t="s">
+        <v>362</v>
       </c>
       <c r="B154" t="s">
         <v>201</v>
@@ -8884,8 +8633,8 @@
       </c>
     </row>
     <row r="155" spans="1:57">
-      <c r="A155" t="s">
-        <v>362</v>
+      <c r="A155" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="B155" t="s">
         <v>161</v>
@@ -8928,8 +8677,8 @@
       </c>
     </row>
     <row r="156" spans="1:57">
-      <c r="A156" t="s">
-        <v>363</v>
+      <c r="A156" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="B156" t="s">
         <v>204</v>
@@ -8996,8 +8745,8 @@
       </c>
     </row>
     <row r="157" spans="1:57">
-      <c r="A157" t="s">
-        <v>364</v>
+      <c r="A157" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="B157" t="s">
         <v>195</v>
@@ -9025,8 +8774,8 @@
       </c>
     </row>
     <row r="158" spans="1:57">
-      <c r="A158" t="s">
-        <v>365</v>
+      <c r="A158" s="1" t="s">
+        <v>366</v>
       </c>
       <c r="B158" t="s">
         <v>162</v>
@@ -9060,8 +8809,8 @@
       </c>
     </row>
     <row r="159" spans="1:57">
-      <c r="A159" t="s">
-        <v>366</v>
+      <c r="A159" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="B159" t="s">
         <v>163</v>
@@ -9093,7 +8842,7 @@
     </row>
     <row r="160" spans="1:57">
       <c r="A160" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="B160" t="s">
         <v>164</v>
@@ -9130,7 +8879,7 @@
       </c>
     </row>
     <row r="161" spans="1:57">
-      <c r="A161" t="s">
+      <c r="A161" s="1" t="s">
         <v>368</v>
       </c>
       <c r="B161" t="s">
@@ -9171,7 +8920,7 @@
       </c>
     </row>
     <row r="162" spans="1:57">
-      <c r="A162" t="s">
+      <c r="A162" s="1" t="s">
         <v>369</v>
       </c>
       <c r="B162" t="s">
@@ -9257,7 +9006,7 @@
       </c>
     </row>
     <row r="163" spans="1:57">
-      <c r="A163" t="s">
+      <c r="A163" s="1" t="s">
         <v>370</v>
       </c>
       <c r="B163" t="s">
@@ -9334,7 +9083,7 @@
       </c>
     </row>
     <row r="164" spans="1:57">
-      <c r="A164" t="s">
+      <c r="A164" s="1" t="s">
         <v>371</v>
       </c>
       <c r="B164" t="s">
@@ -9366,7 +9115,7 @@
       </c>
     </row>
     <row r="165" spans="1:57">
-      <c r="A165" t="s">
+      <c r="A165" s="1" t="s">
         <v>372</v>
       </c>
       <c r="B165" t="s">
@@ -9398,7 +9147,7 @@
       </c>
     </row>
     <row r="166" spans="1:57">
-      <c r="A166" t="s">
+      <c r="A166" s="1" t="s">
         <v>373</v>
       </c>
       <c r="B166" t="s">
@@ -9427,7 +9176,7 @@
       </c>
     </row>
     <row r="167" spans="1:57">
-      <c r="A167" t="s">
+      <c r="A167" s="1" t="s">
         <v>374</v>
       </c>
       <c r="B167" t="s">
@@ -9459,7 +9208,7 @@
       </c>
     </row>
     <row r="168" spans="1:57">
-      <c r="A168" t="s">
+      <c r="A168" s="1" t="s">
         <v>375</v>
       </c>
       <c r="B168" t="s">
@@ -9497,7 +9246,7 @@
       </c>
     </row>
     <row r="169" spans="1:57">
-      <c r="A169" t="s">
+      <c r="A169" s="1" t="s">
         <v>376</v>
       </c>
       <c r="B169" t="s">
@@ -9578,7 +9327,7 @@
     </row>
     <row r="170" spans="1:57">
       <c r="A170" t="s">
-        <v>377</v>
+        <v>319</v>
       </c>
       <c r="B170" t="s">
         <v>174</v>
@@ -9612,8 +9361,8 @@
       </c>
     </row>
     <row r="171" spans="1:57">
-      <c r="A171" t="s">
-        <v>378</v>
+      <c r="A171" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="B171" t="s">
         <v>175</v>
@@ -9644,8 +9393,8 @@
       </c>
     </row>
     <row r="172" spans="1:57">
-      <c r="A172" t="s">
-        <v>379</v>
+      <c r="A172" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="B172" t="s">
         <v>176</v>
@@ -9673,8 +9422,8 @@
       </c>
     </row>
     <row r="173" spans="1:57">
-      <c r="A173" t="s">
-        <v>380</v>
+      <c r="A173" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="B173" t="s">
         <v>177</v>
@@ -9708,8 +9457,8 @@
       </c>
     </row>
     <row r="174" spans="1:57">
-      <c r="A174" t="s">
-        <v>381</v>
+      <c r="A174" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="B174" t="s">
         <v>178</v>
@@ -9743,8 +9492,8 @@
       </c>
     </row>
     <row r="175" spans="1:57">
-      <c r="A175" t="s">
-        <v>382</v>
+      <c r="A175" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="B175" t="s">
         <v>179</v>
@@ -9805,8 +9554,8 @@
       </c>
     </row>
     <row r="176" spans="1:57">
-      <c r="A176" t="s">
-        <v>383</v>
+      <c r="A176" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="B176" t="s">
         <v>180</v>
@@ -9843,8 +9592,8 @@
       </c>
     </row>
     <row r="177" spans="1:57">
-      <c r="A177" t="s">
-        <v>384</v>
+      <c r="A177" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="B177" t="s">
         <v>181</v>
@@ -9884,6 +9633,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A172">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="渡辺">
+      <formula>NOT(ISERROR(SEARCH("渡辺",A172)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/data_shichigawahama_w2.xlsx
+++ b/data/data_shichigawahama_w2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B26730F-D342-4FF1-8490-558C5A84F242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC471EB1-849D-4322-94DB-8022D52632ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,16 +37,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="386">
   <si>
     <t>address_w2</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>district_w2</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -681,9 +677,6 @@
   </si>
   <si>
     <t>吉田浜字大豆沢３－１</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>七ヶ浜町吉田浜字野山１番地の２七ヶ浜第１スポーツ広場応急仮設住宅</t>
@@ -1303,6 +1296,14 @@
   </si>
   <si>
     <t>id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>v13_preferred_farmland_manager_group_farm_w2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>name_w2</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1665,7 +1666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF178"/>
+  <dimension ref="A1:BF177"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="67.4140625" customWidth="1"/>
@@ -1727,178 +1728,178 @@
   <sheetData>
     <row r="1" spans="1:58">
       <c r="A1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1" t="s">
         <v>385</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
-        <v>25</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" t="s">
-        <v>18</v>
-      </c>
-      <c r="W1" t="s">
-        <v>19</v>
-      </c>
-      <c r="X1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
+        <v>384</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AV1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>46</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>47</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>48</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>49</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>50</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>51</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>52</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>53</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>54</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:58">
@@ -1906,10 +1907,10 @@
         <v>100</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D2">
         <v>5</v>
@@ -1983,10 +1984,10 @@
         <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -2024,10 +2025,10 @@
         <v>195</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -2071,10 +2072,10 @@
         <v>162</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -2109,10 +2110,10 @@
         <v>164</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -2162,10 +2163,10 @@
         <v>166</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -2212,10 +2213,10 @@
         <v>167</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -2265,10 +2266,10 @@
         <v>168</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -2327,10 +2328,10 @@
         <v>130</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -2365,10 +2366,10 @@
         <v>170</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -2418,10 +2419,10 @@
         <v>171</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12">
         <v>7</v>
@@ -2459,10 +2460,10 @@
         <v>173</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13">
         <v>7</v>
@@ -2515,10 +2516,10 @@
         <v>174</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -2562,10 +2563,10 @@
         <v>132</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -2606,10 +2607,10 @@
         <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -2638,10 +2639,10 @@
         <v>231</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -2670,10 +2671,10 @@
         <v>51</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -2711,10 +2712,10 @@
         <v>52</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -2788,10 +2789,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -2826,10 +2827,10 @@
         <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D21">
         <v>4</v>
@@ -2867,10 +2868,10 @@
         <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22">
         <v>4</v>
@@ -2899,10 +2900,10 @@
         <v>175</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D23">
         <v>7</v>
@@ -2940,10 +2941,10 @@
         <v>177</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C24" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D24">
         <v>7</v>
@@ -2981,10 +2982,10 @@
         <v>134</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C25" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -3025,10 +3026,10 @@
         <v>136</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D26">
         <v>6</v>
@@ -3069,10 +3070,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -3113,10 +3114,10 @@
         <v>196</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D28">
         <v>8</v>
@@ -3154,10 +3155,10 @@
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -3201,10 +3202,10 @@
         <v>109</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -3233,10 +3234,10 @@
         <v>114</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -3268,10 +3269,10 @@
         <v>115</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C32" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -3318,10 +3319,10 @@
         <v>137</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D33">
         <v>6</v>
@@ -3362,10 +3363,10 @@
         <v>138</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -3394,10 +3395,10 @@
         <v>139</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C35" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -3471,10 +3472,10 @@
         <v>9</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -3512,10 +3513,10 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -3586,10 +3587,10 @@
         <v>12</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -3624,10 +3625,10 @@
         <v>116</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D39">
         <v>5</v>
@@ -3668,10 +3669,10 @@
         <v>13</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D40">
         <v>3</v>
@@ -3715,10 +3716,10 @@
         <v>141</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -3759,10 +3760,10 @@
         <v>142</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D42">
         <v>6</v>
@@ -3809,10 +3810,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D43">
         <v>3</v>
@@ -3844,10 +3845,10 @@
         <v>55</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -3897,10 +3898,10 @@
         <v>232</v>
       </c>
       <c r="B45" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D45">
         <v>7</v>
@@ -3959,10 +3960,10 @@
         <v>179</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D46">
         <v>7</v>
@@ -4036,10 +4037,10 @@
         <v>56</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D47">
         <v>4</v>
@@ -4098,10 +4099,10 @@
         <v>15</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D48">
         <v>3</v>
@@ -4136,10 +4137,10 @@
         <v>181</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C49" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D49">
         <v>7</v>
@@ -4198,10 +4199,10 @@
         <v>182</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D50">
         <v>7</v>
@@ -4272,10 +4273,10 @@
         <v>183</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51">
         <v>7</v>
@@ -4304,10 +4305,10 @@
         <v>185</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D52">
         <v>7</v>
@@ -4369,10 +4370,10 @@
         <v>187</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D53">
         <v>7</v>
@@ -4410,10 +4411,10 @@
         <v>220</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D54">
         <v>9</v>
@@ -4442,10 +4443,10 @@
         <v>221</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D55">
         <v>9</v>
@@ -4483,10 +4484,10 @@
         <v>222</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D56">
         <v>8</v>
@@ -4530,10 +4531,10 @@
         <v>233</v>
       </c>
       <c r="B57" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D57">
         <v>7</v>
@@ -4565,10 +4566,10 @@
         <v>224</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D58">
         <v>8</v>
@@ -4603,10 +4604,10 @@
         <v>225</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -4677,10 +4678,10 @@
         <v>226</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D60">
         <v>9</v>
@@ -4718,10 +4719,10 @@
         <v>234</v>
       </c>
       <c r="B61" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D61">
         <v>9</v>
@@ -4753,10 +4754,10 @@
         <v>197</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D62">
         <v>8</v>
@@ -4791,10 +4792,10 @@
         <v>227</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C63" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D63">
         <v>9</v>
@@ -4829,10 +4830,10 @@
         <v>198</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D64">
         <v>8</v>
@@ -4864,10 +4865,10 @@
         <v>189</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D65">
         <v>7</v>
@@ -4938,10 +4939,10 @@
         <v>190</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C66" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D66">
         <v>7</v>
@@ -5003,10 +5004,10 @@
         <v>229</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D67">
         <v>9</v>
@@ -5038,10 +5039,10 @@
         <v>235</v>
       </c>
       <c r="B68" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C68" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D68">
         <v>4</v>
@@ -5073,10 +5074,10 @@
         <v>199</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C69" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D69">
         <v>8</v>
@@ -5111,10 +5112,10 @@
         <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D70">
         <v>6</v>
@@ -5155,10 +5156,10 @@
         <v>191</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C71" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D71">
         <v>6</v>
@@ -5226,10 +5227,10 @@
         <v>117</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D72">
         <v>5</v>
@@ -5291,10 +5292,10 @@
         <v>60</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -5347,10 +5348,10 @@
         <v>236</v>
       </c>
       <c r="B74" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D74">
         <v>6</v>
@@ -5382,10 +5383,10 @@
         <v>143</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D75">
         <v>5</v>
@@ -5420,10 +5421,10 @@
         <v>2</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -5458,10 +5459,10 @@
         <v>144</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D77">
         <v>5</v>
@@ -5496,10 +5497,10 @@
         <v>118</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D78">
         <v>5</v>
@@ -5537,10 +5538,10 @@
         <v>237</v>
       </c>
       <c r="B79" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D79">
         <v>4</v>
@@ -5578,10 +5579,10 @@
         <v>18</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -5613,10 +5614,10 @@
         <v>145</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C81" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D81">
         <v>6</v>
@@ -5657,10 +5658,10 @@
         <v>146</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D82">
         <v>6</v>
@@ -5692,10 +5693,10 @@
         <v>19</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -5733,10 +5734,10 @@
         <v>20</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -5771,10 +5772,10 @@
         <v>62</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C85" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D85">
         <v>4</v>
@@ -5812,10 +5813,10 @@
         <v>21</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -5844,10 +5845,10 @@
         <v>22</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D87">
         <v>3</v>
@@ -5897,10 +5898,10 @@
         <v>156</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D88">
         <v>5</v>
@@ -5935,10 +5936,10 @@
         <v>119</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D89">
         <v>5</v>
@@ -5973,10 +5974,10 @@
         <v>23</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D90">
         <v>3</v>
@@ -6011,10 +6012,10 @@
         <v>120</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C91" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D91">
         <v>5</v>
@@ -6055,10 +6056,10 @@
         <v>121</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C92" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D92">
         <v>5</v>
@@ -6126,10 +6127,10 @@
         <v>122</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C93" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D93">
         <v>5</v>
@@ -6200,10 +6201,10 @@
         <v>25</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C94" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -6241,10 +6242,10 @@
         <v>151</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C95" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D95">
         <v>6</v>
@@ -6285,10 +6286,10 @@
         <v>152</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C96" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D96">
         <v>6</v>
@@ -6329,10 +6330,10 @@
         <v>153</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C97" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D97">
         <v>6</v>
@@ -6373,10 +6374,10 @@
         <v>155</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C98" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D98">
         <v>6</v>
@@ -6420,10 +6421,10 @@
         <v>26</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C99" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -6497,10 +6498,10 @@
         <v>27</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -6535,10 +6536,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C101" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -6573,10 +6574,10 @@
         <v>28</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D102">
         <v>3</v>
@@ -6608,10 +6609,10 @@
         <v>123</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C103" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D103">
         <v>5</v>
@@ -6679,10 +6680,10 @@
         <v>17</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C104" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -6717,10 +6718,10 @@
         <v>201</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D105">
         <v>8</v>
@@ -6755,10 +6756,10 @@
         <v>203</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C106" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D106">
         <v>8</v>
@@ -6793,10 +6794,10 @@
         <v>230</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C107" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D107">
         <v>9</v>
@@ -6831,10 +6832,10 @@
         <v>30</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C108" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -6881,10 +6882,10 @@
         <v>64</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C109" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D109">
         <v>4</v>
@@ -6925,10 +6926,10 @@
         <v>124</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C110" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D110">
         <v>5</v>
@@ -6975,10 +6976,10 @@
         <v>192</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C111" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D111">
         <v>7</v>
@@ -7031,10 +7032,10 @@
         <v>157</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C112" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D112">
         <v>5</v>
@@ -7075,10 +7076,10 @@
         <v>158</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D113">
         <v>6</v>
@@ -7110,10 +7111,10 @@
         <v>159</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C114" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D114">
         <v>6</v>
@@ -7169,10 +7170,10 @@
         <v>5</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -7207,10 +7208,10 @@
         <v>66</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C116" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -7263,10 +7264,10 @@
         <v>32</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C117" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D117">
         <v>3</v>
@@ -7295,10 +7296,10 @@
         <v>204</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C118" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D118">
         <v>8</v>
@@ -7336,10 +7337,10 @@
         <v>4</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C119" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D119">
         <v>2</v>
@@ -7374,10 +7375,10 @@
         <v>67</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C120" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -7439,10 +7440,10 @@
         <v>205</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C121" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D121">
         <v>8</v>
@@ -7477,10 +7478,10 @@
         <v>34</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C122" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D122">
         <v>3</v>
@@ -7566,10 +7567,10 @@
         <v>238</v>
       </c>
       <c r="B123" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C123" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D123">
         <v>4</v>
@@ -7607,10 +7608,10 @@
         <v>35</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C124" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D124">
         <v>3</v>
@@ -7648,10 +7649,10 @@
         <v>206</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C125" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D125">
         <v>8</v>
@@ -7692,10 +7693,10 @@
         <v>36</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D126">
         <v>3</v>
@@ -7736,10 +7737,10 @@
         <v>37</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C127" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D127">
         <v>3</v>
@@ -7771,10 +7772,10 @@
         <v>38</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C128" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D128">
         <v>3</v>
@@ -7809,10 +7810,10 @@
         <v>39</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C129" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D129">
         <v>3</v>
@@ -7844,10 +7845,10 @@
         <v>73</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C130" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D130">
         <v>4</v>
@@ -7882,10 +7883,10 @@
         <v>49</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C131" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -7935,10 +7936,10 @@
         <v>44</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C132" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D132">
         <v>3</v>
@@ -7979,10 +7980,10 @@
         <v>126</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C133" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D133">
         <v>5</v>
@@ -8035,10 +8036,10 @@
         <v>45</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C134" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -8082,10 +8083,10 @@
         <v>127</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C135" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D135">
         <v>5</v>
@@ -8162,10 +8163,10 @@
         <v>128</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C136" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D136">
         <v>5</v>
@@ -8212,10 +8213,10 @@
         <v>74</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C137" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D137">
         <v>4</v>
@@ -8268,10 +8269,10 @@
         <v>75</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C138" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -8306,10 +8307,10 @@
         <v>47</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C139" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -8347,10 +8348,10 @@
         <v>193</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C140" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D140">
         <v>7</v>
@@ -8382,10 +8383,10 @@
         <v>194</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C141" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D141">
         <v>7</v>
@@ -8465,10 +8466,10 @@
         <v>209</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C142" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D142">
         <v>8</v>
@@ -8509,10 +8510,10 @@
         <v>210</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C143" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D143">
         <v>8</v>
@@ -8547,10 +8548,10 @@
         <v>211</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D144">
         <v>8</v>
@@ -8585,10 +8586,10 @@
         <v>212</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D145">
         <v>8</v>
@@ -8632,10 +8633,10 @@
         <v>214</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C146" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D146">
         <v>8</v>
@@ -8670,10 +8671,10 @@
         <v>215</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C147" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D147">
         <v>8</v>
@@ -8711,10 +8712,10 @@
         <v>48</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C148" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D148">
         <v>3</v>
@@ -8752,10 +8753,10 @@
         <v>77</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C149" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D149">
         <v>4</v>
@@ -8817,10 +8818,10 @@
         <v>78</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C150" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D150">
         <v>4</v>
@@ -8873,10 +8874,10 @@
         <v>79</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C151" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D151">
         <v>4</v>
@@ -8908,10 +8909,10 @@
         <v>82</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C152" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D152">
         <v>4</v>
@@ -8940,10 +8941,10 @@
         <v>88</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C153" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D153">
         <v>4</v>
@@ -9017,10 +9018,10 @@
         <v>90</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C154" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D154">
         <v>4</v>
@@ -9094,10 +9095,10 @@
         <v>160</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C155" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D155">
         <v>6</v>
@@ -9141,10 +9142,10 @@
         <v>94</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C156" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D156">
         <v>4</v>
@@ -9212,10 +9213,10 @@
         <v>95</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C157" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -9244,10 +9245,10 @@
         <v>97</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C158" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D158">
         <v>4</v>
@@ -9282,10 +9283,10 @@
         <v>6</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C159" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -9317,10 +9318,10 @@
         <v>239</v>
       </c>
       <c r="B160" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C160" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D160">
         <v>8</v>
@@ -9358,10 +9359,10 @@
         <v>99</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D161">
         <v>4</v>
@@ -9402,10 +9403,10 @@
         <v>110</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C162" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D162">
         <v>5</v>
@@ -9491,10 +9492,10 @@
         <v>71</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C163" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D163">
         <v>5</v>
@@ -9571,10 +9572,10 @@
         <v>147</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C164" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D164">
         <v>6</v>
@@ -9606,10 +9607,10 @@
         <v>148</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C165" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D165">
         <v>6</v>
@@ -9641,10 +9642,10 @@
         <v>46</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C166" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D166">
         <v>3</v>
@@ -9673,10 +9674,10 @@
         <v>176</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C167" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D167">
         <v>7</v>
@@ -9708,10 +9709,10 @@
         <v>133</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C168" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D168">
         <v>5</v>
@@ -9749,10 +9750,10 @@
         <v>93</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D169">
         <v>4</v>
@@ -9832,10 +9833,10 @@
         <v>240</v>
       </c>
       <c r="B170" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C170" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D170">
         <v>3</v>
@@ -9870,10 +9871,10 @@
         <v>172</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D171">
         <v>7</v>
@@ -9905,10 +9906,10 @@
         <v>57</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C172" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D172">
         <v>4</v>
@@ -9937,10 +9938,10 @@
         <v>40</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C173" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D173">
         <v>2</v>
@@ -9975,10 +9976,10 @@
         <v>129</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C174" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D174">
         <v>5</v>
@@ -10013,10 +10014,10 @@
         <v>186</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C175" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D175">
         <v>7</v>
@@ -10078,10 +10079,10 @@
         <v>41</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C176" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D176">
         <v>3</v>
@@ -10119,10 +10120,10 @@
         <v>11</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C177" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D177">
         <v>3</v>
@@ -10150,11 +10151,6 @@
       </c>
       <c r="BF177">
         <v>2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:58">
-      <c r="C178" t="s">
-        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_shichigawahama_w2.xlsx
+++ b/data/data_shichigawahama_w2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4E8707-67A8-4267-A86C-7FE3082450D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8543F2C9-DB41-44F5-BEC0-D521CC16D9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
